--- a/downloads/indicadores/INPP/INPP_datos.xlsx
+++ b/downloads/indicadores/INPP/INPP_datos.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U109"/>
+  <dimension ref="A1:U110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -520,7 +520,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf · Fecha de publicación: 07 de agosto de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf · Fecha de publicación: 07 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U6" s="8" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="T7" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U7" s="11" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U8" s="8" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="T9" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U9" s="11" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U10" s="8" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="T11" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U11" s="11" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U12" s="8" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="T13" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U13" s="11" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U14" s="8" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="T15" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U15" s="11" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U16" s="8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="T17" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U17" s="11" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="T19" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U19" s="11" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U20" s="8" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="T21" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U21" s="11" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U22" s="8" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T23" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U23" s="11" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="T25" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U25" s="11" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="T27" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U27" s="11" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U28" s="8" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="T29" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U29" s="11" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U30" s="8" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="T31" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U31" s="11" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U32" s="8" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="T33" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U33" s="11" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U34" s="8" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="T35" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U35" s="11" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U36" s="8" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="T37" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U37" s="11" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U38" s="8" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="T39" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U39" s="11" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U40" s="8" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="T41" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U41" s="11" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U42" s="8" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="T43" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U43" s="11" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U44" s="8" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="T45" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U45" s="11" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U46" s="8" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="T47" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U47" s="11" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U48" s="8" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="T49" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U49" s="11" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U50" s="8" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U52" s="8" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="T53" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U53" s="11" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U54" s="8" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="T55" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U55" s="11" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U56" s="8" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="T57" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U57" s="11" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U58" s="8" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="T59" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U59" s="11" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U60" s="8" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="T61" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U61" s="11" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U62" s="8" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="T63" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U63" s="11" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U64" s="8" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="T65" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U65" s="11" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="T66" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U66" s="8" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="T67" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U67" s="11" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="T68" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U68" s="8" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="T69" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U69" s="11" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="T70" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U70" s="8" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="T71" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U71" s="11" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="T72" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U72" s="8" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="T73" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U73" s="11" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="T74" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U74" s="8" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="T75" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U75" s="11" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="T76" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U76" s="8" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="T77" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U77" s="11" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="T78" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U78" s="8" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="T79" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U79" s="11" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="T80" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U80" s="8" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="T81" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U81" s="11" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="T82" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U82" s="8" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="T83" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U83" s="11" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="T84" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U84" s="8" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="T85" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U85" s="11" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="T86" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U86" s="8" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="T87" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U87" s="11" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="T88" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U88" s="8" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="T89" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U89" s="11" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="T90" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U90" s="8" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="T91" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U91" s="11" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="T92" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U92" s="8" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="T93" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U93" s="11" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="T94" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U94" s="8" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="T95" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U95" s="11" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="T96" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U96" s="8" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="T97" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U97" s="11" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="T98" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U98" s="8" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="T99" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U99" s="11" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="T100" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U100" s="8" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="T101" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U101" s="11" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="T102" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U102" s="8" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="T103" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U103" s="11" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="T104" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U104" s="8" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="T105" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U105" s="11" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="T106" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U106" s="8" t="inlineStr">
@@ -8056,7 +8056,7 @@
         <v>46174</v>
       </c>
       <c r="C107" s="9" t="n">
-        <v>135.289726</v>
+        <v>135.282308</v>
       </c>
       <c r="D107" s="10" t="n">
         <v>-0.8714460000000001</v>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="T107" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U107" s="11" t="inlineStr">
@@ -8131,7 +8131,7 @@
         <v>46204</v>
       </c>
       <c r="C108" s="6" t="n">
-        <v>135.185239</v>
+        <v>135.233066</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>-0.077232</v>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="T108" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U108" s="8" t="inlineStr">
@@ -8206,16 +8206,16 @@
         <v>46235</v>
       </c>
       <c r="C109" s="9" t="n">
-        <v>135.268388</v>
+        <v>135.129533</v>
       </c>
       <c r="D109" s="10" t="n">
-        <v>0.061508</v>
+        <v>-0.076559</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>2.988427</v>
+        <v>2.882708</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>1.607483</v>
+        <v>1.503181</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>135.70328</v>
@@ -8239,7 +8239,7 @@
         <v>-2.499552</v>
       </c>
       <c r="N109" s="10" t="n">
-        <v>13.088118</v>
+        <v>10.564728</v>
       </c>
       <c r="O109" s="10" t="n">
         <v>5.907611</v>
@@ -8262,10 +8262,85 @@
       </c>
       <c r="T109" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
         </is>
       </c>
       <c r="U109" s="11" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>136.976422</v>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>1.366754</v>
+      </c>
+      <c r="E110" s="7" t="n">
+        <v>4.052856</v>
+      </c>
+      <c r="F110" s="7" t="n">
+        <v>2.89048</v>
+      </c>
+      <c r="G110" s="6" t="n">
+        <v>136.779878</v>
+      </c>
+      <c r="H110" s="7" t="n">
+        <v>0.793347</v>
+      </c>
+      <c r="I110" s="7" t="n">
+        <v>3.3572</v>
+      </c>
+      <c r="J110" s="7" t="n">
+        <v>1.976231</v>
+      </c>
+      <c r="K110" s="7" t="n">
+        <v>3.176662</v>
+      </c>
+      <c r="L110" s="7" t="n">
+        <v>0.855777</v>
+      </c>
+      <c r="M110" s="7" t="n">
+        <v>0.855777</v>
+      </c>
+      <c r="N110" s="7" t="n">
+        <v>23.84357</v>
+      </c>
+      <c r="O110" s="7" t="n">
+        <v>5.712014</v>
+      </c>
+      <c r="P110" s="7" t="n">
+        <v>2.484374</v>
+      </c>
+      <c r="Q110" s="7" t="n">
+        <v>5.862128</v>
+      </c>
+      <c r="R110" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="S110" s="8" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="T110" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="U110" s="8" t="inlineStr">
         <is>
           <t>07 de agosto de 2026</t>
         </is>

--- a/downloads/indicadores/INPP/INPP_datos.xlsx
+++ b/downloads/indicadores/INPP/INPP_datos.xlsx
@@ -520,7 +520,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf · Fecha de publicación: 07 de agosto de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf · Fecha de publicación: 07 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U6" s="8" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="T7" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U7" s="11" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U8" s="8" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="T9" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U9" s="11" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U10" s="8" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="T11" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U11" s="11" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U12" s="8" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="T13" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U13" s="11" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U14" s="8" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="T15" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U15" s="11" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U16" s="8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="T17" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U17" s="11" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="T19" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U19" s="11" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U20" s="8" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="T21" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U21" s="11" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U22" s="8" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T23" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U23" s="11" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="T25" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U25" s="11" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="T27" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U27" s="11" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U28" s="8" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="T29" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U29" s="11" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U30" s="8" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="T31" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U31" s="11" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U32" s="8" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="T33" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U33" s="11" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U34" s="8" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="T35" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U35" s="11" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U36" s="8" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="T37" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U37" s="11" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U38" s="8" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="T39" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U39" s="11" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U40" s="8" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="T41" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U41" s="11" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U42" s="8" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="T43" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U43" s="11" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U44" s="8" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="T45" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U45" s="11" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U46" s="8" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="T47" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U47" s="11" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U48" s="8" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="T49" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U49" s="11" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U50" s="8" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="T51" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U51" s="11" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U52" s="8" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="T53" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U53" s="11" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U54" s="8" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="T55" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U55" s="11" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U56" s="8" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="T57" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U57" s="11" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U58" s="8" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="T59" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U59" s="11" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U60" s="8" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="T61" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U61" s="11" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U62" s="8" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="T63" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U63" s="11" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U64" s="8" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="T65" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U65" s="11" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="T66" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U66" s="8" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="T67" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U67" s="11" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="T68" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U68" s="8" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="T69" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U69" s="11" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="T70" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U70" s="8" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="T71" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U71" s="11" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="T72" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U72" s="8" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="T73" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U73" s="11" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="T74" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U74" s="8" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="T75" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U75" s="11" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="T76" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U76" s="8" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="T77" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U77" s="11" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="T78" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U78" s="8" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="T79" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U79" s="11" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="T80" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U80" s="8" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="T81" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U81" s="11" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="T82" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U82" s="8" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="T83" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U83" s="11" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="T84" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U84" s="8" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="T85" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U85" s="11" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="T86" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U86" s="8" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="T87" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U87" s="11" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="T88" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U88" s="8" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="T89" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U89" s="11" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="T90" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U90" s="8" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="T91" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U91" s="11" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="T92" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U92" s="8" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="T93" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U93" s="11" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="T94" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U94" s="8" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="T95" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U95" s="11" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="T96" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U96" s="8" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="T97" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U97" s="11" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="T98" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U98" s="8" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="T99" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U99" s="11" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="T100" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U100" s="8" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="T101" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U101" s="11" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="T102" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U102" s="8" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="T103" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U103" s="11" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="T104" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U104" s="8" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="T105" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U105" s="11" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="T106" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U106" s="8" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="T107" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U107" s="11" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="T108" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U108" s="8" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="T109" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U109" s="11" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="T110" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpp/inpp2026_10.pdf</t>
         </is>
       </c>
       <c r="U110" s="8" t="inlineStr">
